--- a/results/Int Task Remove ACC 0.5/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_8_permute.xlsx
@@ -440,377 +440,377 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8325219995072616</v>
+        <v>0.8302004434645829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8315573692821812</v>
+        <v>0.8276104081516624</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8286104144688217</v>
+        <v>0.8158225888982242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8380943657256206</v>
+        <v>0.8174656820321038</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8499175610711376</v>
+        <v>0.8204126368454634</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.840486673952457</v>
+        <v>0.8023739884648671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8401651305440969</v>
+        <v>0.7895861628942697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.830518828293293</v>
+        <v>0.8063209495953859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8285541917510534</v>
+        <v>0.8069994125041851</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6952836088667648</v>
+        <v>0.8069994125041851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6916935672366851</v>
+        <v>0.8069994125041851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6874427507438455</v>
+        <v>0.811338669227222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.690389705557205</v>
+        <v>0.7926215579378265</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6752803239439289</v>
+        <v>0.7909784648039471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6301113715184556</v>
+        <v>0.7880668860826663</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6317721526983746</v>
+        <v>0.7801729638216287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6281821110682948</v>
+        <v>0.7772260090082692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6140727357721779</v>
+        <v>0.7733144239698293</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6131081055470976</v>
+        <v>0.7743321183330281</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.580263930915546</v>
+        <v>0.7651520224385497</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5920694382150234</v>
+        <v>0.7553288397273514</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5920694382150234</v>
+        <v>0.751399566642872</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5865324480887435</v>
+        <v>0.7808868028225068</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.514823214296995</v>
+        <v>0.7808868028225068</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5052685108560383</v>
+        <v>0.764205080259509</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4996961446376793</v>
+        <v>0.7144814559788755</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5039469611305188</v>
+        <v>0.7036759549965572</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5039469611305188</v>
+        <v>0.6896019557925193</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5046077359932786</v>
+        <v>0.6912627369724382</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5026254114049994</v>
+        <v>0.6230904806726512</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5023038679966393</v>
+        <v>0.6342882772474874</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5039469611305188</v>
+        <v>0.6336451904307672</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5039469611305188</v>
+        <v>0.6336451904307672</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5042685045388789</v>
+        <v>0.6228396894484488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5042685045388789</v>
+        <v>0.6228396894484488</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5059115976727585</v>
+        <v>0.5898009463104631</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5068939159438783</v>
+        <v>0.5898009463104631</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5068939159438783</v>
+        <v>0.5191624710200318</v>
       </c>
     </row>
     <row r="40">
@@ -820,327 +820,327 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5006607748627597</v>
+        <v>0.5131801211631154</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5134309123873178</v>
+        <v>0.513519352617515</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5104839575739581</v>
+        <v>0.513519352617515</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.505572366218359</v>
+        <v>0.512215490938035</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5088585524861181</v>
+        <v>0.5050000315857965</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5114839638911174</v>
+        <v>0.5050000315857965</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5033038743137986</v>
+        <v>0.5050000315857965</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5101801022116375</v>
+        <v>0.5092331600325966</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5059292857187979</v>
+        <v>0.5125193463003557</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5059292857187979</v>
+        <v>0.5030000189514779</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5105016456199976</v>
+        <v>0.5034100025900353</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5078762342149982</v>
+        <v>0.4942652827876361</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5016430931338796</v>
+        <v>0.4926398776997959</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4843151251745115</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4892267165301107</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.487654375580389</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4895482599384709</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5009823182711198</v>
+        <v>0.4920675430672335</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5009823182711198</v>
+        <v>0.4936575720629947</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5009823182711198</v>
+        <v>0.4930144852462744</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5009823182711198</v>
+        <v>0.4943183469257544</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5009823182711198</v>
+        <v>0.4978022602795975</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5</v>
+        <v>0.4939968035173943</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4997492087757977</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4994099773213981</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.5000530641381183</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.495569144467116</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4980707395498392</v>
+        <v>0.495961440059634</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.5037492340444349</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.505731558632714</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.5013569258175983</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4993569131832797</v>
+        <v>0.5014099899557167</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4990353697749196</v>
+        <v>0.5023746201807971</v>
       </c>
     </row>
     <row r="73">
@@ -1150,67 +1150,67 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.499053057820959</v>
+        <v>0.5027669157733151</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.499053057820959</v>
+        <v>0.4997492087757977</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5000176880460395</v>
+        <v>0.5010353824092382</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5000176880460395</v>
+        <v>0.5010353824092382</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5006607748627597</v>
+        <v>0.4997492087757977</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.4987668905046779</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4996784565916399</v>
+        <v>0.501660781179919</v>
       </c>
     </row>
     <row r="80">
@@ -1220,107 +1220,107 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5003392314543996</v>
+        <v>0.5053038869481171</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5010000063171594</v>
+        <v>0.4997315207297582</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5010000063171594</v>
+        <v>0.4996961446376793</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5016430931338796</v>
+        <v>0.4996961446376793</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5013215497255195</v>
+        <v>0.4996961446376793</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5016430931338796</v>
+        <v>0.4977668841875185</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5019646365422397</v>
+        <v>0.4977668841875185</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5006784629087991</v>
+        <v>0.4993569131832797</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5006784629087991</v>
+        <v>0.4996961446376793</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5006784629087991</v>
+        <v>0.5006607748627597</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5023215560426787</v>
+        <v>0.5006607748627597</v>
       </c>
     </row>
   </sheetData>
